--- a/testdata/EMD_Workbook.xlsx
+++ b/testdata/EMD_Workbook.xlsx
@@ -659,18 +659,18 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="34" t="n">
-        <v>117.0</v>
+        <v>122.0</v>
       </c>
       <c r="B2" s="34" t="n">
         <v>100.0</v>
       </c>
       <c r="C2" s="34">
         <f>A2*B2*10</f>
-        <v>102000</v>
+        <v>110000</v>
       </c>
       <c r="D2" s="3">
         <f>C2*0.001</f>
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="E2" s="3">
         <f>B2*0</f>
@@ -681,102 +681,102 @@
       </c>
       <c r="G2" s="3">
         <f>C2*0.0003</f>
-        <v>30.599999999999998</v>
+        <v>33</v>
       </c>
       <c r="H2" s="3">
         <f>G2*0.18</f>
-        <v>5.5079999999999991</v>
+        <v>5.9399999999999995</v>
       </c>
       <c r="I2" s="3">
         <f>C2*0.049</f>
-        <v>4998</v>
+        <v>5390</v>
       </c>
       <c r="J2" s="4">
         <f>(D2+E2+G2+H2+I2)*10</f>
-        <v>51361.08</v>
+        <v>55389.399999999994</v>
       </c>
       <c r="K2" s="5" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="6" t="n">
-        <v>117.0</v>
-      </c>
-      <c r="B3" s="6" t="n">
-        <v>100.0</v>
+      <c r="A3" s="6">
+        <v>104</v>
+      </c>
+      <c r="B3" s="6">
+        <v>100</v>
       </c>
       <c r="C3" s="6">
         <f>A3*B3*10</f>
-        <v>12000</v>
+        <v>104000</v>
       </c>
       <c r="D3" s="6">
         <f>C3*0.001</f>
-        <v>12</v>
+        <v>104</v>
       </c>
       <c r="E3" s="6">
         <f>C3*0.005</f>
-        <v>60</v>
+        <v>520</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>10</v>
       </c>
       <c r="G3" s="6">
         <f>C3*0.001</f>
-        <v>12</v>
+        <v>104</v>
       </c>
       <c r="H3" s="6">
         <f>G3*0.18</f>
-        <v>2.16</v>
+        <v>18.72</v>
       </c>
       <c r="I3" s="6">
         <f>C3*0.044</f>
-        <v>528</v>
+        <v>4576</v>
       </c>
       <c r="J3" s="7">
         <f>D3+E3+G3+H3+I3</f>
-        <v>614.16</v>
+        <v>5322.72</v>
       </c>
       <c r="K3" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="8" t="n">
-        <v>117.0</v>
-      </c>
-      <c r="B4" s="8" t="n">
-        <v>100.0</v>
+      <c r="A4" s="8">
+        <v>105</v>
+      </c>
+      <c r="B4" s="8">
+        <v>100</v>
       </c>
       <c r="C4" s="8">
         <f>A4*B4*10</f>
-        <v>700000</v>
+        <v>105000</v>
       </c>
       <c r="D4" s="8">
         <f>C4*0.001</f>
-        <v>700</v>
+        <v>105</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>10</v>
       </c>
       <c r="F4" s="9">
         <f>C4*0.03</f>
-        <v>21000</v>
+        <v>3150</v>
       </c>
       <c r="G4" s="8">
         <f>C4*0.0035</f>
-        <v>2450</v>
+        <v>367.5</v>
       </c>
       <c r="H4" s="10">
         <f>G4*0.18</f>
-        <v>441</v>
+        <v>66.149999999999991</v>
       </c>
       <c r="I4" s="11" t="s">
         <v>10</v>
       </c>
       <c r="J4" s="10">
         <f>D4+F4</f>
-        <v>21700</v>
+        <v>3255</v>
       </c>
       <c r="K4" s="12" t="s">
         <v>13</v>

--- a/testdata/EMD_Workbook.xlsx
+++ b/testdata/EMD_Workbook.xlsx
@@ -659,18 +659,18 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="34" t="n">
-        <v>122.0</v>
+        <v>126.0</v>
       </c>
       <c r="B2" s="34" t="n">
         <v>100.0</v>
       </c>
       <c r="C2" s="34">
         <f>A2*B2*10</f>
-        <v>110000</v>
+        <v>125000</v>
       </c>
       <c r="D2" s="3">
         <f>C2*0.001</f>
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="E2" s="3">
         <f>B2*0</f>
@@ -681,19 +681,19 @@
       </c>
       <c r="G2" s="3">
         <f>C2*0.0003</f>
-        <v>33</v>
+        <v>37.5</v>
       </c>
       <c r="H2" s="3">
         <f>G2*0.18</f>
-        <v>5.9399999999999995</v>
+        <v>6.75</v>
       </c>
       <c r="I2" s="3">
         <f>C2*0.049</f>
-        <v>5390</v>
+        <v>6125</v>
       </c>
       <c r="J2" s="4">
         <f>(D2+E2+G2+H2+I2)*10</f>
-        <v>55389.399999999994</v>
+        <v>62942.5</v>
       </c>
       <c r="K2" s="5" t="s">
         <v>11</v>

--- a/testdata/EMD_Workbook.xlsx
+++ b/testdata/EMD_Workbook.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="164011"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\eclipse-workspace\automation\testdata\"/>
     </mc:Choice>
@@ -14,9 +14,9 @@
   <sheets>
     <sheet name="EMDCalculation" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913" fullCalcOnLoad="true"/>
+  <calcPr calcId="162913"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -280,9 +280,6 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="2" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -326,6 +323,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -611,18 +611,18 @@
   <dimension ref="A1:L19"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="2" width="11.140625"/>
-    <col min="2" max="2" customWidth="true" style="2" width="15.28515625"/>
-    <col min="3" max="3" customWidth="true" style="2" width="17.5703125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="2" width="14.42578125"/>
-    <col min="5" max="5" customWidth="true" style="2" width="15.140625"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="2" width="17.42578125"/>
-    <col min="7" max="7" customWidth="true" style="2" width="21.5703125"/>
-    <col min="8" max="8" customWidth="true" style="2" width="18.42578125"/>
-    <col min="9" max="9" customWidth="true" style="2" width="22.140625"/>
-    <col min="10" max="10" customWidth="true" style="2" width="19.42578125"/>
-    <col min="11" max="11" customWidth="true" style="2" width="23.7109375"/>
-    <col min="12" max="16384" style="2" width="8.7109375"/>
+    <col min="1" max="1" width="11.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="15.28515625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="17.5703125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.140625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="17.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.5703125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="18.42578125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="22.140625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="19.42578125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="23.7109375" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="8.7109375" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -658,19 +658,19 @@
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="34" t="n">
-        <v>126.0</v>
-      </c>
-      <c r="B2" s="34" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="C2" s="34">
+      <c r="A2" s="33">
+        <v>100</v>
+      </c>
+      <c r="B2" s="33">
+        <v>100</v>
+      </c>
+      <c r="C2" s="33">
         <f>A2*B2*10</f>
-        <v>125000</v>
+        <v>100000</v>
       </c>
       <c r="D2" s="3">
         <f>C2*0.001</f>
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="E2" s="3">
         <f>B2*0</f>
@@ -681,19 +681,19 @@
       </c>
       <c r="G2" s="3">
         <f>C2*0.0003</f>
-        <v>37.5</v>
+        <v>29.999999999999996</v>
       </c>
       <c r="H2" s="3">
         <f>G2*0.18</f>
-        <v>6.75</v>
+        <v>5.3999999999999995</v>
       </c>
       <c r="I2" s="3">
         <f>C2*0.049</f>
-        <v>6125</v>
+        <v>4900</v>
       </c>
       <c r="J2" s="4">
         <f>(D2+E2+G2+H2+I2)*10</f>
-        <v>62942.5</v>
+        <v>50354</v>
       </c>
       <c r="K2" s="5" t="s">
         <v>11</v>
@@ -701,41 +701,41 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="6">
-        <v>104</v>
+        <v>1015</v>
       </c>
       <c r="B3" s="6">
         <v>100</v>
       </c>
       <c r="C3" s="6">
         <f>A3*B3*10</f>
-        <v>104000</v>
+        <v>1015000</v>
       </c>
       <c r="D3" s="6">
         <f>C3*0.001</f>
-        <v>104</v>
+        <v>1015</v>
       </c>
       <c r="E3" s="6">
         <f>C3*0.005</f>
-        <v>520</v>
+        <v>5075</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>10</v>
       </c>
       <c r="G3" s="6">
         <f>C3*0.001</f>
-        <v>104</v>
+        <v>1015</v>
       </c>
       <c r="H3" s="6">
         <f>G3*0.18</f>
-        <v>18.72</v>
+        <v>182.7</v>
       </c>
       <c r="I3" s="6">
         <f>C3*0.044</f>
-        <v>4576</v>
+        <v>44660</v>
       </c>
       <c r="J3" s="7">
         <f>D3+E3+G3+H3+I3</f>
-        <v>5322.72</v>
+        <v>51947.7</v>
       </c>
       <c r="K3" s="5" t="s">
         <v>12</v>
@@ -743,42 +743,42 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="8">
-        <v>105</v>
+        <v>1013</v>
       </c>
       <c r="B4" s="8">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="C4" s="8">
         <f>A4*B4*10</f>
-        <v>105000</v>
+        <v>5065000</v>
       </c>
       <c r="D4" s="8">
         <f>C4*0.001</f>
-        <v>105</v>
+        <v>5065</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="9">
-        <f>C4*0.03</f>
-        <v>3150</v>
+      <c r="F4" s="34">
+        <f>(C4*0.03)*10</f>
+        <v>1519500</v>
       </c>
       <c r="G4" s="8">
         <f>C4*0.0035</f>
-        <v>367.5</v>
-      </c>
-      <c r="H4" s="10">
+        <v>17727.5</v>
+      </c>
+      <c r="H4" s="9">
         <f>G4*0.18</f>
-        <v>66.149999999999991</v>
-      </c>
-      <c r="I4" s="11" t="s">
+        <v>3190.95</v>
+      </c>
+      <c r="I4" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="10">
+      <c r="J4" s="9">
         <f>D4+F4</f>
-        <v>3255</v>
-      </c>
-      <c r="K4" s="12" t="s">
+        <v>1524565</v>
+      </c>
+      <c r="K4" s="11" t="s">
         <v>13</v>
       </c>
     </row>
@@ -808,153 +808,153 @@
         <f>C5*0.0005</f>
         <v>52.5</v>
       </c>
-      <c r="H5" s="10">
+      <c r="H5" s="9">
         <f>G5*0.18</f>
         <v>9.4499999999999993</v>
       </c>
-      <c r="I5" s="13" t="s">
+      <c r="I5" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="10">
+      <c r="J5" s="9">
         <f>D5+F5+G5+H5</f>
         <v>3316.95</v>
       </c>
-      <c r="K5" s="12" t="s">
+      <c r="K5" s="11" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="14">
+      <c r="A6" s="13">
         <v>10</v>
       </c>
-      <c r="B6" s="14">
+      <c r="B6" s="13">
         <v>200</v>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="13">
         <f>A6*B6*10</f>
         <v>20000</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="13">
         <f>C6*0.001</f>
         <v>20</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="13">
         <f>B6*0</f>
         <v>0</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="F6" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="14">
+      <c r="G6" s="13">
         <f>C6*0.0003</f>
         <v>5.9999999999999991</v>
       </c>
-      <c r="H6" s="14">
+      <c r="H6" s="13">
         <f>G6*0.18</f>
         <v>1.0799999999999998</v>
       </c>
-      <c r="I6" s="14">
+      <c r="I6" s="13">
         <f>C6*0.049</f>
         <v>980</v>
       </c>
-      <c r="J6" s="15">
+      <c r="J6" s="14">
         <f>D6+E6+G6+H6+I6</f>
         <v>1007.08</v>
       </c>
-      <c r="K6" s="16" t="s">
+      <c r="K6" s="15" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:12">
-      <c r="H7" s="17"/>
-      <c r="I7" s="18"/>
-      <c r="K7" s="19"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="17"/>
+      <c r="K7" s="18"/>
     </row>
     <row r="8" spans="1:12">
-      <c r="H8" s="17"/>
-      <c r="I8" s="18"/>
-      <c r="K8" s="19"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="17"/>
+      <c r="K8" s="18"/>
     </row>
     <row r="9" spans="1:12">
-      <c r="G9" s="20"/>
-      <c r="H9" s="21"/>
-      <c r="I9" s="18"/>
-      <c r="K9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="17"/>
+      <c r="K9" s="18"/>
     </row>
     <row r="10" spans="1:12">
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="22"/>
-      <c r="I10" s="23"/>
-      <c r="J10" s="19"/>
-      <c r="K10" s="18"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="18"/>
+      <c r="K10" s="17"/>
     </row>
     <row r="11" spans="1:12">
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="24"/>
-      <c r="H11" s="25"/>
-      <c r="I11" s="26"/>
-      <c r="J11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="23"/>
+      <c r="H11" s="24"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="17"/>
     </row>
     <row r="12" spans="1:12">
-      <c r="E12" s="18"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="24"/>
-      <c r="H12" s="27"/>
-      <c r="I12" s="27"/>
-      <c r="J12" s="18"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="23"/>
+      <c r="H12" s="26"/>
+      <c r="I12" s="26"/>
+      <c r="J12" s="17"/>
     </row>
     <row r="13" spans="1:12">
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="24"/>
-      <c r="I13" s="18"/>
-      <c r="J13" s="18"/>
-      <c r="L13" s="29"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="27"/>
+      <c r="H13" s="23"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="17"/>
+      <c r="L13" s="28"/>
     </row>
     <row r="14" spans="1:12">
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="I14" s="18"/>
-      <c r="J14" s="30"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="29"/>
     </row>
     <row r="15" spans="1:12">
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="18"/>
-      <c r="I15" s="18"/>
-      <c r="J15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="17"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="17"/>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="31"/>
-      <c r="H16" s="28"/>
-      <c r="I16" s="26"/>
-      <c r="J16" s="30"/>
-      <c r="K16" s="32"/>
-      <c r="L16" s="32"/>
+      <c r="A16" s="30"/>
+      <c r="H16" s="27"/>
+      <c r="I16" s="25"/>
+      <c r="J16" s="29"/>
+      <c r="K16" s="31"/>
+      <c r="L16" s="31"/>
     </row>
     <row r="17" spans="2:11">
-      <c r="B17" s="33"/>
-      <c r="C17" s="33"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="26"/>
-      <c r="I17" s="18"/>
-      <c r="J17" s="30"/>
-      <c r="K17" s="30"/>
+      <c r="B17" s="32"/>
+      <c r="C17" s="32"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="25"/>
+      <c r="I17" s="17"/>
+      <c r="J17" s="29"/>
+      <c r="K17" s="29"/>
     </row>
     <row r="18" spans="2:11">
-      <c r="B18" s="33"/>
-      <c r="H18" s="24"/>
-      <c r="I18" s="27"/>
+      <c r="B18" s="32"/>
+      <c r="H18" s="23"/>
+      <c r="I18" s="26"/>
     </row>
     <row r="19" spans="2:11">
-      <c r="B19" s="33"/>
-      <c r="H19" s="24"/>
-      <c r="I19" s="18"/>
+      <c r="B19" s="32"/>
+      <c r="H19" s="23"/>
+      <c r="I19" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
